--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6BC2F4B-10AF-9842-9649-D6F68F3C1698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B396B66D-D135-8542-8DB6-B06DC6AFF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18440" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
   <si>
     <t>Date de naissance</t>
   </si>
@@ -153,6 +153,9 @@
   </si>
   <si>
     <t>O3/09/2006</t>
+  </si>
+  <si>
+    <t>1m88</t>
   </si>
 </sst>
 </file>
@@ -213,142 +216,7 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="14">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="1"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="4" tint="-0.499984740745262"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B0F0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -734,6 +602,9 @@
       <c r="D4" s="1" t="s">
         <v>4</v>
       </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
@@ -870,7 +741,7 @@
         <v>31</v>
       </c>
       <c r="C17" s="2">
-        <v>44926</v>
+        <v>37621</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>17</v>

--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B396B66D-D135-8542-8DB6-B06DC6AFF2EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A59E6E2-4A08-A947-8BA1-74F2A4905970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18440" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
@@ -146,9 +146,6 @@
     <t>Ismail Mediouna</t>
   </si>
   <si>
-    <t xml:space="preserve">Fares </t>
-  </si>
-  <si>
     <t>Donald Onana</t>
   </si>
   <si>
@@ -156,6 +153,9 @@
   </si>
   <si>
     <t>1m88</t>
+  </si>
+  <si>
+    <t>Fares  Farhi</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -664,7 +664,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -813,16 +813,18 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C24" s="2">
+        <v>36752</v>
+      </c>
       <c r="D24" s="1" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C25" s="2">
         <v>37082</v>

--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A59E6E2-4A08-A947-8BA1-74F2A4905970}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEEF851-E090-644E-897B-7636D48F46D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="18440" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
@@ -134,9 +134,6 @@
     <t>Sandro Marcon</t>
   </si>
   <si>
-    <t xml:space="preserve">Bradley </t>
-  </si>
-  <si>
     <t>Pharell Cafara</t>
   </si>
   <si>
@@ -156,6 +153,9 @@
   </si>
   <si>
     <t>Fares  Farhi</t>
+  </si>
+  <si>
+    <t>Brady Gouandjia</t>
   </si>
 </sst>
 </file>
@@ -603,7 +603,7 @@
         <v>4</v>
       </c>
       <c r="E4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
@@ -664,7 +664,7 @@
         <v>28</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -771,16 +771,18 @@
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
-        <v>32</v>
-      </c>
-      <c r="C20" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="C20" s="2">
+        <v>38750</v>
+      </c>
       <c r="D20" s="1" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C21" s="2">
         <v>39746</v>
@@ -791,7 +793,7 @@
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C22" s="2">
         <v>39185</v>
@@ -802,7 +804,7 @@
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C23" s="2">
         <v>37673</v>
@@ -813,7 +815,7 @@
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" s="2">
         <v>36752</v>
@@ -824,7 +826,7 @@
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C25" s="2">
         <v>37082</v>

--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAEEF851-E090-644E-897B-7636D48F46D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5FFBF-4BD8-354B-B848-1363B1A2DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="18440" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
+    <workbookView xWindow="4260" yWindow="700" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
   <si>
     <t>Date de naissance</t>
   </si>
@@ -156,6 +156,18 @@
   </si>
   <si>
     <t>Brady Gouandjia</t>
+  </si>
+  <si>
+    <t>Romain Antunes</t>
+  </si>
+  <si>
+    <t>Kamal Bafounta</t>
+  </si>
+  <si>
+    <t>1m87</t>
+  </si>
+  <si>
+    <t>1m92</t>
   </si>
 </sst>
 </file>
@@ -198,7 +210,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -211,6 +223,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -546,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC62179-91BA-B241-B8B8-EFBF1E6AE721}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -627,12 +642,17 @@
       <c r="D6" s="1" t="s">
         <v>14</v>
       </c>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="C7" s="2"/>
+      <c r="C7" s="2">
+        <v>39484</v>
+      </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
       </c>
@@ -736,7 +756,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>31</v>
       </c>
@@ -747,7 +767,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>22</v>
       </c>
@@ -758,7 +778,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>13</v>
       </c>
@@ -769,7 +789,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>39</v>
       </c>
@@ -780,7 +800,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
@@ -791,7 +811,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -802,7 +822,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
@@ -813,7 +833,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>38</v>
       </c>
@@ -824,7 +844,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>35</v>
       </c>
@@ -835,7 +855,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -844,6 +864,31 @@
       </c>
       <c r="D26" s="1" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="5">
+        <v>36726</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="5">
+        <v>37264</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
       </c>
     </row>
   </sheetData>

--- a/data/2026-2027/Informations joueurs.xlsx
+++ b/data/2026-2027/Informations joueurs.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/christophergallo/Desktop/Application perso/data/2026-2027/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C5FFBF-4BD8-354B-B848-1363B1A2DB33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6932281-9DC5-E44A-8648-133058B4D585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4260" yWindow="700" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
+    <workbookView xWindow="4260" yWindow="500" windowWidth="10360" windowHeight="16360" xr2:uid="{88726A7A-4B88-8C42-AD00-6D2620F5EC74}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
   <si>
     <t>Date de naissance</t>
   </si>
@@ -168,6 +168,15 @@
   </si>
   <si>
     <t>1m92</t>
+  </si>
+  <si>
+    <t>Sofiane Belkheir</t>
+  </si>
+  <si>
+    <t>Brian Chevreuil</t>
+  </si>
+  <si>
+    <t>Marc Thomas</t>
   </si>
 </sst>
 </file>
@@ -561,7 +570,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BC62179-91BA-B241-B8B8-EFBF1E6AE721}">
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.5" customWidth="1"/>
@@ -891,6 +900,21 @@
         <v>43</v>
       </c>
     </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
